--- a/Forecasts/Forecast-29062026-0Z.xlsx
+++ b/Forecasts/Forecast-29062026-0Z.xlsx
@@ -653,7 +653,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 29/06/2026 09:17</t>
+          <t>Généré le : 29/06/2026 11:48</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 29/06/2026 09:17</t>
+          <t>Généré le : 29/06/2026 11:48</t>
         </is>
       </c>
     </row>

--- a/Forecasts/Forecast-29062026-0Z.xlsx
+++ b/Forecasts/Forecast-29062026-0Z.xlsx
@@ -653,7 +653,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 29/06/2026 11:48</t>
+          <t>Généré le : 30/06/2026 08:07</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 29/06/2026 11:48</t>
+          <t>Généré le : 30/06/2026 08:07</t>
         </is>
       </c>
     </row>
